--- a/artfynd/A 36225-2024 artfynd.xlsx
+++ b/artfynd/A 36225-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1761360</v>
+        <v>589117</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444675.5825073134</v>
+        <v>444676</v>
       </c>
       <c r="R2" t="n">
-        <v>6433445.15496072</v>
+        <v>6433445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,14 @@
           <t>2011-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I vägkanten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>589117</v>
+        <v>90693783</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,46 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hökensås, Svedån, Vg</t>
+          <t>Hökensås NVO, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444675.5825073134</v>
+        <v>444511</v>
       </c>
       <c r="R3" t="n">
-        <v>6433445.15496072</v>
+        <v>6433371</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-09-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I vägkanten</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,31 +867,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Emma Roland</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1673543</v>
+        <v>90693806</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,46 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hökensås, Svedån, Vg</t>
+          <t>Hökensås NVO, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444675.5825073134</v>
+        <v>444644</v>
       </c>
       <c r="R4" t="n">
-        <v>6433445.15496072</v>
+        <v>6433372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,66 +973,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Emma Roland</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90003800</v>
+        <v>90693785</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hökensås (NVO) S, Vg</t>
+          <t>Hökensås NVO, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444574.1185632563</v>
+        <v>444497</v>
       </c>
       <c r="R5" t="n">
-        <v>6433434.915597729</v>
+        <v>6433373</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1085,6 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1165,15 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90003799</v>
+        <v>90693799</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hökensås (NVO) S, Vg</t>
+          <t>Hökensås NVO, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444479.8655938008</v>
+        <v>444485</v>
       </c>
       <c r="R6" t="n">
-        <v>6433409.223313997</v>
+        <v>6433378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1191,6 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1287,19 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90003807</v>
+        <v>90003799</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1327,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444620.0629797709</v>
+        <v>444480</v>
       </c>
       <c r="R7" t="n">
-        <v>6433419.981152159</v>
+        <v>6433409</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,19 +1278,9 @@
           <t>2020-10-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,7 +1306,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Roland, Helena Bager</t>
+          <t>Helena Bager, Emma Roland</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1409,19 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90003805</v>
+        <v>90003800</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1449,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444670.2493493989</v>
+        <v>444574</v>
       </c>
       <c r="R8" t="n">
-        <v>6433443.111048792</v>
+        <v>6433435</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,19 +1385,9 @@
           <t>2020-10-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1413,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Roland, Helena Bager</t>
+          <t>Helena Bager, Emma Roland</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1531,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90003826</v>
+        <v>90003805</v>
       </c>
       <c r="B9" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444526.900286851</v>
+        <v>444670</v>
       </c>
       <c r="R9" t="n">
-        <v>6433358.267246674</v>
+        <v>6433443</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1604,19 +1492,9 @@
           <t>2020-10-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,7 +1520,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Roland, Helena Bager</t>
+          <t>Helena Bager, Emma Roland</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1653,50 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90693794</v>
+        <v>90003807</v>
       </c>
       <c r="B10" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hökensås NVO, Vg</t>
+          <t>Hökensås (NVO) S, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444353.9687176156</v>
+        <v>444620</v>
       </c>
       <c r="R10" t="n">
-        <v>6433472.927725001</v>
+        <v>6433420</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1723,22 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,6 +1618,7 @@
           <t>Sandtallskog</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1763,7 +1627,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Roland, Helena Bager</t>
+          <t>Helena Bager, Emma Roland</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1774,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90693801</v>
+        <v>90003810</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1810,14 +1669,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hökensås NVO, Vg</t>
+          <t>Hökensås (NVO) S, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444492.7345447452</v>
+        <v>444475</v>
       </c>
       <c r="R11" t="n">
-        <v>6433380.981328266</v>
+        <v>6433384</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1844,22 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,6 +1725,7 @@
           <t>Sandtallskog</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1884,7 +1734,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Roland, Helena Bager</t>
+          <t>Helena Bager, Emma Roland</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1898,16 +1748,11 @@
         <v>90693768</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1935,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444620.9840363397</v>
+        <v>444621</v>
       </c>
       <c r="R12" t="n">
-        <v>6433409.908168147</v>
+        <v>6433410</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1968,19 +1813,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,15 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>90693783</v>
+        <v>90693795</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444511.1654384015</v>
+        <v>444448</v>
       </c>
       <c r="R13" t="n">
-        <v>6433371.193975153</v>
+        <v>6433399</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2089,19 +1919,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2130,6 +1950,2246 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>90693796</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444454</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433393</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>90693801</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>444493</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433381</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>90693794</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>444354</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433473</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>90693787</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>444438</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433406</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>90693800</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>444485</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433379</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1761360</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hökensås, Svedån, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>444676</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433445</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2011-09-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2011-09-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>90003802</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>444673</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433479</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>90003803</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>444678</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433463</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>90003804</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>444677</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433465</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>90003809</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>444490</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433376</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>90003812</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>444454</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433393</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>90003814</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>444449</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433396</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>90003816</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>444333</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433475</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>90003826</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>444527</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433358</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>90003827</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>444535</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433351</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>90003828</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>444542</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433345</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>90003829</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>444559</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6433349</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>90003830</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>444408</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6433424</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>90003831</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>444391</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6433436</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>90003832</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hökensås (NVO) S, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>444356</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6433457</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Helena Bager, Emma Roland</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>90693788</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hökensås NVO, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>444352</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6433467</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Härja</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
         <is>
           <t>Sandbarrskog Västra Götaland</t>
         </is>

--- a/artfynd/A 36225-2024 artfynd.xlsx
+++ b/artfynd/A 36225-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/589117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693806</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003800</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003807</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003810</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693768</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693795</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693796</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693801</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693794</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693787</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693800</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1761360</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,6 +2792,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003802</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2804,6 +2904,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003803</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2911,6 +3016,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003804</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3018,6 +3128,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003809</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3125,6 +3240,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003812</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3232,6 +3352,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003814</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3339,6 +3464,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003816</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3446,6 +3576,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003826</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3553,6 +3688,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003827</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3660,6 +3800,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003828</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3767,6 +3912,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003829</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3874,6 +4024,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003830</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3981,6 +4136,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003831</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4088,6 +4248,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003832</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4194,8 +4359,48 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90693788</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>